--- a/data/trans_dic/P32E$amigos_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32E$amigos_2023-Clase-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,49; 57,9</t>
+          <t>9,87; 56,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,88</t>
+          <t>0,0; 81,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,32; 53,66</t>
+          <t>10,23; 52,82</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,6; 53,31</t>
+          <t>7,3; 53,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,28; 68,61</t>
+          <t>7,55; 69,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,41; 52,72</t>
+          <t>15,0; 52,57</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 30,82</t>
+          <t>2,95; 29,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,56</t>
+          <t>2,84; 28,73</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,54; 37,54</t>
+          <t>6,63; 36,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 37,06</t>
+          <t>1,54; 35,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,02; 31,31</t>
+          <t>8,07; 34,68</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,11; 57,23</t>
+          <t>17,81; 59,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,34; 74,55</t>
+          <t>13,85; 74,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,09; 56,79</t>
+          <t>22,31; 57,22</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,64</t>
+          <t>0,0; 41,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,83</t>
+          <t>0,0; 47,49</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,48; 33,01</t>
+          <t>16,56; 33,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,75; 37,4</t>
+          <t>12,44; 37,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,36; 31,69</t>
+          <t>17,02; 31,32</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2014; 11117</t>
+          <t>1895; 10765</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5099</t>
+          <t>0; 5100</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2878; 13644</t>
+          <t>2600; 13430</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1037; 7272</t>
+          <t>996; 7325</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1312; 7976</t>
+          <t>877; 8062</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3641; 13320</t>
+          <t>3791; 13283</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>820; 9026</t>
+          <t>863; 8566</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 672</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 8364</t>
+          <t>893; 9045</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2531; 14518</t>
+          <t>2564; 14112</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>168; 3934</t>
+          <t>163; 3748</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3953; 15430</t>
+          <t>3976; 17092</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5989; 18929</t>
+          <t>5892; 19577</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1241; 6030</t>
+          <t>1120; 6030</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9092; 23376</t>
+          <t>9183; 23557</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4906</t>
+          <t>0; 5004</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 9885</t>
+          <t>0; 8886</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>23158; 46386</t>
+          <t>23269; 46678</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6482; 19007</t>
+          <t>6321; 19064</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33212; 60639</t>
+          <t>32573; 59928</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$amigos_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P32E$amigos_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,87; 56,07</t>
+          <t>11,36; 57,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,9</t>
+          <t>0,0; 78,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,23; 52,82</t>
+          <t>12,73; 55,6</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 53,7</t>
+          <t>6,99; 53,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 69,35</t>
+          <t>10,43; 64,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15,0; 52,57</t>
+          <t>15,67; 52,03</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 29,25</t>
+          <t>2,41; 27,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 28,73</t>
+          <t>2,6; 24,62</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 36,49</t>
+          <t>6,45; 36,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 35,31</t>
+          <t>4,62; 59,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,07; 34,68</t>
+          <t>9,69; 34,06</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>41,61%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>17,81; 59,19</t>
+          <t>18,51; 59,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,85; 74,54</t>
+          <t>14,09; 72,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,31; 57,22</t>
+          <t>23,15; 58,48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 91,79</t>
+          <t>0,0; 89,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,45</t>
+          <t>0,0; 43,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,49</t>
+          <t>0,0; 40,6</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,56; 33,22</t>
+          <t>16,87; 34,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12,44; 37,51</t>
+          <t>13,51; 39,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,02; 31,32</t>
+          <t>17,66; 32,42</t>
         </is>
       </c>
     </row>
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7818</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1895; 10765</t>
+          <t>2322; 11774</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5100</t>
+          <t>0; 5116</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2600; 13430</t>
+          <t>3425; 14962</t>
         </is>
       </c>
     </row>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4969</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>9154</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>996; 7325</t>
+          <t>1071; 8187</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>877; 8062</t>
+          <t>1396; 8673</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3791; 13283</t>
+          <t>4498; 14936</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3347</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>863; 8566</t>
+          <t>769; 8685</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>893; 9045</t>
+          <t>923; 8743</t>
         </is>
       </c>
     </row>
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>7278</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>11054</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2564; 14112</t>
+          <t>2696; 15186</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>163; 3748</t>
+          <t>685; 8760</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3976; 17092</t>
+          <t>5490; 19294</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15179</t>
+          <t>19071</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1324,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5892; 19577</t>
+          <t>7787; 25229</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1120; 6030</t>
+          <t>1190; 6160</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9183; 23557</t>
+          <t>11694; 29545</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>993</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2485</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 6092</t>
+          <t>0; 5464</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5004</t>
+          <t>0; 5902</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 8886</t>
+          <t>0; 7972</t>
         </is>
       </c>
     </row>
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>52929</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>23269; 46678</t>
+          <t>26600; 53642</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6321; 19064</t>
+          <t>8137; 23850</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>32573; 59928</t>
+          <t>38486; 70654</t>
         </is>
       </c>
     </row>
